--- a/data/viviendas_iniciadas_terminadas_españa_1991_2025.xlsx
+++ b/data/viviendas_iniciadas_terminadas_españa_1991_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iicadic-my.sharepoint.com/personal/pablo_haya_iic_uam_es/Documents/devel/periodismo-de-datos/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_6DDBDCDC8F79A8D366075C52F37BD2725A46D83F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38F59A4C-B5CA-4689-ABB9-ABD82CA0F1B8}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_6DDBDCDC8F79A8D366075C52F37BD2725A46D83F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11DD9BE5-78B5-4531-B97F-3AC5C5D9142B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -549,6 +549,7 @@
   <dimension ref="A1:D666"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.1796875" bestFit="1" customWidth="1"/>
   </cols>
